--- a/TestData/T2279_TMTI0036293_91_92_93_95_97_98_ApproveEventExpenseFormAsSecondLevelApprover.xlsx
+++ b/TestData/T2279_TMTI0036293_91_92_93_95_97_98_ApproveEventExpenseFormAsSecondLevelApprover.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C10B4C4-4746-4CDD-B446-05264B263F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903496ED-D4C5-4EEF-8A84-AB465109DF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExpenseRequest" sheetId="1" r:id="rId1"/>
@@ -183,7 +183,7 @@
     <t>8000.0</t>
   </si>
   <si>
-    <t>Bingo@123456</t>
+    <t>Bingo@12345</t>
   </si>
 </sst>
 </file>
@@ -1014,10 +1014,10 @@
     <hyperlink ref="A4" r:id="rId2" xr:uid="{6ED0707E-1A3D-41DE-9D1F-0C185E1F4903}"/>
     <hyperlink ref="A5" r:id="rId3" xr:uid="{A88A08DE-BC8D-44F4-B4A3-F3F45BEED893}"/>
     <hyperlink ref="B2" r:id="rId4" xr:uid="{88D13356-CD0F-4958-BE46-AB501B49D616}"/>
-    <hyperlink ref="B3" r:id="rId5" xr:uid="{0C4E5F7A-199B-44E4-9D61-A72EC878705A}"/>
-    <hyperlink ref="B4" r:id="rId6" xr:uid="{86E2AB91-5475-4A32-A0B6-24F80795CEF9}"/>
-    <hyperlink ref="B5" r:id="rId7" xr:uid="{8BBDADB2-F7D7-48B9-A02D-97E76879A177}"/>
-    <hyperlink ref="B6" r:id="rId8" xr:uid="{87F05E24-278F-44B1-8C83-DD76224C519C}"/>
+    <hyperlink ref="B3" r:id="rId5" xr:uid="{A3E22827-39FB-4FC6-9EAC-DE7315BA0C81}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{40CE1B5F-D441-448A-B738-F06B6852272B}"/>
+    <hyperlink ref="B5" r:id="rId7" xr:uid="{9113FABB-0C3A-4289-8CE2-6D7F89AA21FC}"/>
+    <hyperlink ref="B6" r:id="rId8" xr:uid="{DF18B413-84D1-46B9-BEF6-EAE88CF2CB16}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1102,10 +1102,10 @@
     <hyperlink ref="A5" r:id="rId2" xr:uid="{49CDF971-88A0-478A-9ABD-0C13B137739B}"/>
     <hyperlink ref="A6" r:id="rId3" xr:uid="{DD33285A-BEC3-43E6-9CF7-C07B547F86A0}"/>
     <hyperlink ref="B2" r:id="rId4" xr:uid="{E884574A-2EFB-4087-B99B-32D65C06622B}"/>
-    <hyperlink ref="B3" r:id="rId5" xr:uid="{6FDB6FAE-2678-4D0A-844A-D0E0F7D83FE8}"/>
-    <hyperlink ref="B4" r:id="rId6" xr:uid="{63848CA5-DB2C-4AE0-AEAA-FE709617B998}"/>
-    <hyperlink ref="B5" r:id="rId7" xr:uid="{449ECCB6-ADD3-49DB-B00C-07186A4B0F38}"/>
-    <hyperlink ref="B6" r:id="rId8" xr:uid="{91A2AD90-3E91-42F8-A59E-0B11EED9136A}"/>
+    <hyperlink ref="B3" r:id="rId5" xr:uid="{6105F52E-E972-4C98-B334-0EDCFCF9DD32}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{DD20A5EF-1467-4F63-9B7E-9F173DA3A144}"/>
+    <hyperlink ref="B5" r:id="rId7" xr:uid="{37C79583-FD74-4201-9420-A533782C49EB}"/>
+    <hyperlink ref="B6" r:id="rId8" xr:uid="{889EEB08-DA51-4093-ADBB-2B4F74F1E660}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
